--- a/BADesign/Excel/Reward.xlsx
+++ b/BADesign/Excel/Reward.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.293.56114"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="570" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="560" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Reward" sheetId="1" r:id="rId1"/>
@@ -985,7 +985,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
     <col min="2" max="2" width="16.75499916" customWidth="1" outlineLevel="0"/>
@@ -1080,6 +1080,48 @@
         <v>3</v>
       </c>
     </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2">
+        <v>502</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2">
+        <v>502</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
